--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="177">
   <si>
     <t>Property</t>
   </si>
@@ -69,21 +69,6 @@
   </si>
   <si>
     <t>Publisher</t>
-  </si>
-  <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -694,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -777,60 +762,42 @@
       <c r="A10" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>18</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>19</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>24</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -845,1218 +812,1218 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>32</v>
-      </c>
       <c r="D1" t="s" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E93" s="2"/>
     </row>
@@ -2072,516 +2039,516 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>32</v>
-      </c>
       <c r="D1" t="s" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -2597,48 +2564,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>32</v>
-      </c>
       <c r="D1" t="s" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="176">
   <si>
     <t>Property</t>
   </si>
@@ -83,16 +83,13 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS</t>
+  </si>
+  <si>
     <t>Source</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS</t>
   </si>
   <si>
     <t>Display</t>
@@ -679,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -790,14 +787,6 @@
       </c>
       <c r="B14" t="s" s="2">
         <v>23</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -812,1218 +801,1218 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>22</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>24</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>30</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E93" s="2"/>
     </row>
@@ -2039,516 +2028,516 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>22</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>24</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>30</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -2564,48 +2553,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>22</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>24</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="178">
   <si>
     <t>Property</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>Publisher</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -676,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -773,20 +779,28 @@
       <c r="A12" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -801,1218 +815,1218 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>24</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>22</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E93" s="2"/>
     </row>
@@ -2028,516 +2042,516 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>24</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>22</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -2553,48 +2567,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>24</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>22</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240426120000</t>
+    <t>20250415120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-26T12:00:00+01:00</t>
+    <t>2025-04-15T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -230,6 +230,9 @@
     <t>34875-5</t>
   </si>
   <si>
+    <t>34876-3</t>
+  </si>
+  <si>
     <t>39256-3</t>
   </si>
   <si>
@@ -311,6 +314,9 @@
     <t>68599-0</t>
   </si>
   <si>
+    <t>68814-3</t>
+  </si>
+  <si>
     <t>68817-6</t>
   </si>
   <si>
@@ -443,9 +449,6 @@
     <t>CERT_DECL</t>
   </si>
   <si>
-    <t>CONTACTS-URGENCE</t>
-  </si>
-  <si>
     <t>DISP_AUT</t>
   </si>
   <si>
@@ -486,9 +489,6 @@
   </si>
   <si>
     <t>DOCPAT09</t>
-  </si>
-  <si>
-    <t>DOCPAT10</t>
   </si>
   <si>
     <t>IMG-KOS</t>
@@ -810,7 +810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1298,20 +1298,20 @@
         <v>33</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E38" s="2"/>
     </row>
@@ -1324,7 +1324,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -1337,7 +1337,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -1376,7 +1376,7 @@
         <v>33</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E43" s="2"/>
     </row>
@@ -1389,7 +1389,7 @@
         <v>33</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1402,7 +1402,7 @@
         <v>33</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E45" s="2"/>
     </row>
@@ -1441,7 +1441,7 @@
         <v>33</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E48" s="2"/>
     </row>
@@ -1480,7 +1480,7 @@
         <v>33</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E51" s="2"/>
     </row>
@@ -1493,7 +1493,7 @@
         <v>33</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="E52" s="2"/>
     </row>
@@ -1506,7 +1506,7 @@
         <v>33</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -1519,7 +1519,7 @@
         <v>33</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -1532,7 +1532,7 @@
         <v>33</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E55" s="2"/>
     </row>
@@ -1545,7 +1545,7 @@
         <v>33</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -1558,7 +1558,7 @@
         <v>33</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -1571,7 +1571,7 @@
         <v>33</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E58" s="2"/>
     </row>
@@ -1584,7 +1584,7 @@
         <v>33</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1636,33 +1636,33 @@
         <v>33</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="E65" s="2"/>
     </row>
@@ -1675,7 +1675,7 @@
         <v>33</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E66" s="2"/>
     </row>
@@ -1727,7 +1727,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E70" s="2"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E71" s="2"/>
     </row>
@@ -1753,7 +1753,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E72" s="2"/>
     </row>
@@ -1766,7 +1766,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E73" s="2"/>
     </row>
@@ -1779,7 +1779,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E74" s="2"/>
     </row>
@@ -1792,33 +1792,33 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="E77" s="2"/>
     </row>
@@ -1831,7 +1831,7 @@
         <v>33</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E78" s="2"/>
     </row>
@@ -1844,7 +1844,7 @@
         <v>33</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E79" s="2"/>
     </row>
@@ -1857,7 +1857,7 @@
         <v>33</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -1883,7 +1883,7 @@
         <v>33</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -1896,7 +1896,7 @@
         <v>33</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E83" s="2"/>
     </row>
@@ -1909,7 +1909,7 @@
         <v>33</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -1922,7 +1922,7 @@
         <v>33</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -1935,7 +1935,7 @@
         <v>33</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -1948,7 +1948,7 @@
         <v>33</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -1961,7 +1961,7 @@
         <v>33</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E88" s="2"/>
     </row>
@@ -1974,7 +1974,7 @@
         <v>33</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E89" s="2"/>
     </row>
@@ -1987,7 +1987,7 @@
         <v>33</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -2000,7 +2000,7 @@
         <v>33</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -2013,7 +2013,7 @@
         <v>33</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -2026,9 +2026,35 @@
         <v>33</v>
       </c>
       <c r="D93" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B94" s="2"/>
+      <c r="C94" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D94" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="E93" s="2"/>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E95" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2037,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2059,7 +2085,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2076,72 +2102,72 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -2154,7 +2180,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2167,137 +2193,137 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2310,124 +2336,124 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>48</v>
+        <v>161</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2440,20 +2466,20 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -2466,7 +2492,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2479,7 +2505,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2492,7 +2518,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2505,55 +2531,29 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E37" s="2"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="B39" s="2"/>
-      <c r="C39" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E39" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="180">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250415120000</t>
+    <t>20250623120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-15T12:00:00+01:00</t>
+    <t>2025-06-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -423,6 +423,12 @@
   </si>
   <si>
     <t>96173-0</t>
+  </si>
+  <si>
+    <t>97694-4</t>
+  </si>
+  <si>
+    <t>100967-9</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
@@ -810,7 +816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2055,6 +2061,32 @@
         <v>36</v>
       </c>
       <c r="E95" s="2"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B96" s="2"/>
+      <c r="C96" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B97" s="2"/>
+      <c r="C97" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E97" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2085,7 +2117,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2102,7 +2134,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -2115,7 +2147,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -2128,7 +2160,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -2141,7 +2173,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2154,7 +2186,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -2167,7 +2199,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -2180,7 +2212,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2193,7 +2225,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -2206,7 +2238,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -2219,7 +2251,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -2232,7 +2264,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2245,7 +2277,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -2258,7 +2290,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2271,7 +2303,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2284,7 +2316,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2297,7 +2329,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2310,7 +2342,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2323,7 +2355,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2336,7 +2368,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2349,7 +2381,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2362,7 +2394,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -2375,7 +2407,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2388,7 +2420,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -2401,20 +2433,20 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2427,7 +2459,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2440,7 +2472,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -2453,7 +2485,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2466,7 +2498,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2479,7 +2511,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -2492,7 +2524,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2505,7 +2537,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2518,7 +2550,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2531,20 +2563,20 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -2584,7 +2616,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2593,7 +2625,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>30</v>
@@ -2601,14 +2633,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="187">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250623120000</t>
+    <t>20251028120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T12:00:00+01:00</t>
+    <t>2025-10-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -308,6 +308,12 @@
     <t>61357-0</t>
   </si>
   <si>
+    <t>61358-8</t>
+  </si>
+  <si>
+    <t>61359-6</t>
+  </si>
+  <si>
     <t>67851-6</t>
   </si>
   <si>
@@ -389,6 +395,9 @@
     <t>83901-9</t>
   </si>
   <si>
+    <t>83963-9</t>
+  </si>
+  <si>
     <t>83981-1</t>
   </si>
   <si>
@@ -431,6 +440,9 @@
     <t>100967-9</t>
   </si>
   <si>
+    <t>101881-1</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
   <si>
@@ -446,6 +458,9 @@
     <t>ATTEST-DROITS-AM</t>
   </si>
   <si>
+    <t>ATTEST-VITALE</t>
+  </si>
+  <si>
     <t>AUTORIS-SOINS</t>
   </si>
   <si>
@@ -455,6 +470,9 @@
     <t>CERT_DECL</t>
   </si>
   <si>
+    <t>CONTACTS-URGENCE</t>
+  </si>
+  <si>
     <t>DISP_AUT</t>
   </si>
   <si>
@@ -495,6 +513,9 @@
   </si>
   <si>
     <t>DOCPAT09</t>
+  </si>
+  <si>
+    <t>DOCPAT10</t>
   </si>
   <si>
     <t>IMG-KOS</t>
@@ -816,7 +837,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1590,7 +1611,7 @@
         <v>33</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1603,7 +1624,7 @@
         <v>33</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E60" s="2"/>
     </row>
@@ -1668,33 +1689,33 @@
         <v>33</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="E67" s="2"/>
     </row>
@@ -1707,7 +1728,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E68" s="2"/>
     </row>
@@ -1759,7 +1780,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E72" s="2"/>
     </row>
@@ -1772,7 +1793,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E73" s="2"/>
     </row>
@@ -1785,7 +1806,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E74" s="2"/>
     </row>
@@ -1798,7 +1819,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -1811,7 +1832,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E76" s="2"/>
     </row>
@@ -1824,33 +1845,33 @@
         <v>33</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="E79" s="2"/>
     </row>
@@ -1863,7 +1884,7 @@
         <v>33</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -1876,7 +1897,7 @@
         <v>33</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E81" s="2"/>
     </row>
@@ -1889,7 +1910,7 @@
         <v>33</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -1915,7 +1936,7 @@
         <v>33</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -1928,7 +1949,7 @@
         <v>33</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -1941,7 +1962,7 @@
         <v>33</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -1954,7 +1975,7 @@
         <v>33</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -1980,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E89" s="2"/>
     </row>
@@ -1993,7 +2014,7 @@
         <v>33</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -2006,7 +2027,7 @@
         <v>33</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -2019,7 +2040,7 @@
         <v>33</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -2032,7 +2053,7 @@
         <v>33</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E93" s="2"/>
     </row>
@@ -2058,7 +2079,7 @@
         <v>33</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E95" s="2"/>
     </row>
@@ -2084,9 +2105,61 @@
         <v>33</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E97" s="2"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B98" s="2"/>
+      <c r="C98" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B99" s="2"/>
+      <c r="C99" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B100" s="2"/>
+      <c r="C100" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E101" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2095,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2117,7 +2190,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2134,7 +2207,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -2147,7 +2220,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -2160,7 +2233,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -2173,7 +2246,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2186,7 +2259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -2199,98 +2272,98 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2303,46 +2376,46 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2355,150 +2428,150 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2511,20 +2584,20 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2537,7 +2610,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2550,7 +2623,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2563,29 +2636,68 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>174</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D37" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D40" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E40" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2616,7 +2728,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2625,7 +2737,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>30</v>
@@ -2633,14 +2745,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -110,7 +110,7 @@
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A03-ClasseDocument/FHIR/TRE-A03-ClasseDocument</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A03-ClasseDocument/FHIR/TRE-A03-ClasseDocument|20231215120000</t>
   </si>
   <si>
     <t>10213-7</t>
@@ -443,7 +443,7 @@
     <t>101881-1</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire|20240329120000</t>
   </si>
   <si>
     <t>ATTEST-ASS-COMPL</t>
@@ -566,10 +566,10 @@
     <t>FICHE-CONTACTS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A10-NomenclatureURN/FHIR/TRE-A10-NomenclatureURN</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM|20231215120000</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A10-NomenclatureURN/FHIR/TRE-A10-NomenclatureURN|20231215120000</t>
   </si>
   <si>
     <t>E1762</t>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="188">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251028120000</t>
+    <t>20260202120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T12:00:00+01:00</t>
+    <t>2026-02-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>34876-3</t>
+  </si>
+  <si>
+    <t>34895-3</t>
   </si>
   <si>
     <t>39256-3</t>
@@ -837,7 +840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1299,7 +1302,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E35" s="2"/>
     </row>
@@ -1338,20 +1341,20 @@
         <v>33</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -1364,7 +1367,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -1377,7 +1380,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E41" s="2"/>
     </row>
@@ -1416,7 +1419,7 @@
         <v>33</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1429,7 +1432,7 @@
         <v>33</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="E45" s="2"/>
     </row>
@@ -1442,7 +1445,7 @@
         <v>33</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
     </row>
@@ -1481,7 +1484,7 @@
         <v>33</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E49" s="2"/>
     </row>
@@ -1520,7 +1523,7 @@
         <v>33</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E52" s="2"/>
     </row>
@@ -1533,7 +1536,7 @@
         <v>33</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -1546,7 +1549,7 @@
         <v>33</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -1559,7 +1562,7 @@
         <v>33</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E55" s="2"/>
     </row>
@@ -1572,7 +1575,7 @@
         <v>33</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -1585,7 +1588,7 @@
         <v>33</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -1598,7 +1601,7 @@
         <v>33</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E58" s="2"/>
     </row>
@@ -1611,7 +1614,7 @@
         <v>33</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1624,7 +1627,7 @@
         <v>33</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2"/>
     </row>
@@ -1637,7 +1640,7 @@
         <v>33</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="E61" s="2"/>
     </row>
@@ -1650,7 +1653,7 @@
         <v>33</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E62" s="2"/>
     </row>
@@ -1663,7 +1666,7 @@
         <v>33</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E63" s="2"/>
     </row>
@@ -1676,7 +1679,7 @@
         <v>33</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E64" s="2"/>
     </row>
@@ -1689,7 +1692,7 @@
         <v>33</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E65" s="2"/>
     </row>
@@ -1702,7 +1705,7 @@
         <v>33</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E66" s="2"/>
     </row>
@@ -1715,20 +1718,20 @@
         <v>33</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="E68" s="2"/>
     </row>
@@ -1741,7 +1744,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E69" s="2"/>
     </row>
@@ -1806,7 +1809,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E74" s="2"/>
     </row>
@@ -1819,7 +1822,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -1845,7 +1848,7 @@
         <v>33</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E77" s="2"/>
     </row>
@@ -1871,20 +1874,20 @@
         <v>33</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -1910,7 +1913,7 @@
         <v>33</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -1936,7 +1939,7 @@
         <v>33</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -1949,7 +1952,7 @@
         <v>33</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -1975,7 +1978,7 @@
         <v>33</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -2001,7 +2004,7 @@
         <v>33</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E89" s="2"/>
     </row>
@@ -2014,7 +2017,7 @@
         <v>33</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -2027,7 +2030,7 @@
         <v>33</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -2040,7 +2043,7 @@
         <v>33</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -2066,7 +2069,7 @@
         <v>33</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E94" s="2"/>
     </row>
@@ -2079,7 +2082,7 @@
         <v>33</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E95" s="2"/>
     </row>
@@ -2105,7 +2108,7 @@
         <v>33</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E97" s="2"/>
     </row>
@@ -2131,7 +2134,7 @@
         <v>33</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E99" s="2"/>
     </row>
@@ -2157,9 +2160,22 @@
         <v>33</v>
       </c>
       <c r="D101" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E101" s="2"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B102" s="2"/>
+      <c r="C102" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D102" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E102" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2190,7 +2206,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2207,85 +2223,85 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2298,7 +2314,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -2311,20 +2327,20 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -2337,33 +2353,33 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2376,20 +2392,20 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2402,7 +2418,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2415,7 +2431,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2428,7 +2444,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2441,7 +2457,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2454,7 +2470,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2467,7 +2483,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -2480,7 +2496,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2493,33 +2509,33 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2532,7 +2548,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2545,20 +2561,20 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2571,7 +2587,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2584,20 +2600,20 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2610,7 +2626,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2623,7 +2639,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2636,7 +2652,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -2649,7 +2665,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -2662,7 +2678,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -2675,27 +2691,27 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -2728,7 +2744,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -2737,7 +2753,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>30</v>
@@ -2745,14 +2761,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -110,7 +110,7 @@
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A03-ClasseDocument/FHIR/TRE-A03-ClasseDocument|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A03-ClasseDocument/FHIR/TRE-A03-ClasseDocument</t>
   </si>
   <si>
     <t>10213-7</t>
@@ -446,7 +446,7 @@
     <t>101881-1</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire|20240329120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
   <si>
     <t>ATTEST-ASS-COMPL</t>
@@ -569,10 +569,10 @@
     <t>FICHE-CONTACTS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM|20231215120000</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A10-NomenclatureURN/FHIR/TRE-A10-NomenclatureURN|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A10-NomenclatureURN/FHIR/TRE-A10-NomenclatureURN</t>
   </si>
   <si>
     <t>E1762</t>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="190">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260202120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,15 +89,18 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS</t>
+  </si>
+  <si>
     <t>Target</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS</t>
   </si>
   <si>
-    <t>Source</t>
-  </si>
-  <si>
     <t>Display</t>
   </si>
   <si>
@@ -402,6 +405,9 @@
   </si>
   <si>
     <t>83981-1</t>
+  </si>
+  <si>
+    <t>84067-8</t>
   </si>
   <si>
     <t>85208-7</t>
@@ -712,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -833,6 +839,14 @@
         <v>25</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -840,1342 +854,1355 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E102" s="2"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B103" s="2"/>
+      <c r="C103" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E103" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2189,529 +2216,529 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -2727,48 +2754,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="191">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -438,6 +438,9 @@
   </si>
   <si>
     <t>96874-3</t>
+  </si>
+  <si>
+    <t>96163-1</t>
   </si>
   <si>
     <t>96173-0</t>
@@ -854,7 +857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2161,7 +2164,7 @@
         <v>34</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -2174,7 +2177,7 @@
         <v>34</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E101" s="2"/>
     </row>
@@ -2200,9 +2203,22 @@
         <v>34</v>
       </c>
       <c r="D103" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E103" s="2"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B104" s="2"/>
+      <c r="C104" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D104" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="E103" s="2"/>
+      <c r="E104" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2233,7 +2249,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2250,7 +2266,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -2263,7 +2279,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -2276,7 +2292,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -2289,7 +2305,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2302,7 +2318,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -2315,7 +2331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -2328,7 +2344,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2341,7 +2357,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -2354,7 +2370,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -2367,7 +2383,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -2380,7 +2396,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2393,7 +2409,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -2406,7 +2422,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2419,7 +2435,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2432,7 +2448,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2445,7 +2461,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2458,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2471,7 +2487,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2484,7 +2500,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2497,7 +2513,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2510,7 +2526,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -2523,7 +2539,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2536,7 +2552,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -2549,7 +2565,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -2562,7 +2578,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2575,7 +2591,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2588,20 +2604,20 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2614,7 +2630,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2627,7 +2643,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -2640,7 +2656,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2653,7 +2669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2666,7 +2682,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2679,7 +2695,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -2692,7 +2708,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -2705,7 +2721,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -2718,20 +2734,20 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -2771,7 +2787,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2780,7 +2796,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -2788,14 +2804,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/main/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="180">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -233,12 +233,6 @@
     <t>34875-5</t>
   </si>
   <si>
-    <t>34876-3</t>
-  </si>
-  <si>
-    <t>34895-3</t>
-  </si>
-  <si>
     <t>39256-3</t>
   </si>
   <si>
@@ -272,6 +266,9 @@
     <t>56445-0</t>
   </si>
   <si>
+    <t>55751-2</t>
+  </si>
+  <si>
     <t>56446-8</t>
   </si>
   <si>
@@ -314,21 +311,12 @@
     <t>61357-0</t>
   </si>
   <si>
-    <t>61358-8</t>
-  </si>
-  <si>
-    <t>61359-6</t>
-  </si>
-  <si>
     <t>67851-6</t>
   </si>
   <si>
     <t>68599-0</t>
   </si>
   <si>
-    <t>68814-3</t>
-  </si>
-  <si>
     <t>68817-6</t>
   </si>
   <si>
@@ -401,15 +389,9 @@
     <t>83901-9</t>
   </si>
   <si>
-    <t>83963-9</t>
-  </si>
-  <si>
     <t>83981-1</t>
   </si>
   <si>
-    <t>84067-8</t>
-  </si>
-  <si>
     <t>85208-7</t>
   </si>
   <si>
@@ -440,21 +422,9 @@
     <t>96874-3</t>
   </si>
   <si>
-    <t>96163-1</t>
-  </si>
-  <si>
     <t>96173-0</t>
   </si>
   <si>
-    <t>97694-4</t>
-  </si>
-  <si>
-    <t>100967-9</t>
-  </si>
-  <si>
-    <t>101881-1</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
   <si>
@@ -468,9 +438,6 @@
   </si>
   <si>
     <t>ATTEST-DROITS-AM</t>
-  </si>
-  <si>
-    <t>ATTEST-VITALE</t>
   </si>
   <si>
     <t>AUTORIS-SOINS</t>
@@ -857,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1319,7 +1286,7 @@
         <v>34</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2"/>
     </row>
@@ -1345,13 +1312,13 @@
         <v>34</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -1364,14 +1331,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -1384,7 +1351,7 @@
         <v>34</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -1397,7 +1364,7 @@
         <v>34</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2"/>
     </row>
@@ -1423,7 +1390,7 @@
         <v>34</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E43" s="2"/>
     </row>
@@ -1436,7 +1403,7 @@
         <v>34</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1449,7 +1416,7 @@
         <v>34</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E45" s="2"/>
     </row>
@@ -1462,7 +1429,7 @@
         <v>34</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E46" s="2"/>
     </row>
@@ -1501,7 +1468,7 @@
         <v>34</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E49" s="2"/>
     </row>
@@ -1540,7 +1507,7 @@
         <v>34</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E52" s="2"/>
     </row>
@@ -1553,7 +1520,7 @@
         <v>34</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -1566,7 +1533,7 @@
         <v>34</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -1579,7 +1546,7 @@
         <v>34</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E55" s="2"/>
     </row>
@@ -1592,7 +1559,7 @@
         <v>34</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -1605,7 +1572,7 @@
         <v>34</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -1618,7 +1585,7 @@
         <v>34</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E58" s="2"/>
     </row>
@@ -1631,7 +1598,7 @@
         <v>34</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1644,7 +1611,7 @@
         <v>34</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E60" s="2"/>
     </row>
@@ -1657,7 +1624,7 @@
         <v>34</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E61" s="2"/>
     </row>
@@ -1696,26 +1663,26 @@
         <v>34</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -1728,27 +1695,27 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="E68" s="2"/>
     </row>
@@ -1761,7 +1728,7 @@
         <v>34</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E69" s="2"/>
     </row>
@@ -1787,7 +1754,7 @@
         <v>34</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E71" s="2"/>
     </row>
@@ -1800,7 +1767,7 @@
         <v>34</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E72" s="2"/>
     </row>
@@ -1813,7 +1780,7 @@
         <v>34</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E73" s="2"/>
     </row>
@@ -1839,7 +1806,7 @@
         <v>34</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -1852,59 +1819,59 @@
         <v>34</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -1930,7 +1897,7 @@
         <v>34</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -1943,7 +1910,7 @@
         <v>34</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E83" s="2"/>
     </row>
@@ -1956,7 +1923,7 @@
         <v>34</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -1969,7 +1936,7 @@
         <v>34</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -1982,7 +1949,7 @@
         <v>34</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -1995,7 +1962,7 @@
         <v>34</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -2008,7 +1975,7 @@
         <v>34</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E88" s="2"/>
     </row>
@@ -2034,7 +2001,7 @@
         <v>34</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -2047,7 +2014,7 @@
         <v>34</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -2060,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E92" s="2"/>
     </row>
@@ -2073,7 +2040,7 @@
         <v>34</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E93" s="2"/>
     </row>
@@ -2086,139 +2053,9 @@
         <v>34</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E94" s="2"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="B95" s="2"/>
-      <c r="C95" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D95" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="B96" s="2"/>
-      <c r="C96" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D96" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="B97" s="2"/>
-      <c r="C97" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D97" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="B98" s="2"/>
-      <c r="C98" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D98" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="B99" s="2"/>
-      <c r="C99" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D99" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E99" s="2"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="B100" s="2"/>
-      <c r="C100" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D100" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E100" s="2"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="B101" s="2"/>
-      <c r="C101" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D101" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E101" s="2"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B102" s="2"/>
-      <c r="C102" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D102" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E102" s="2"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="B103" s="2"/>
-      <c r="C103" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D103" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E103" s="2"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B104" s="2"/>
-      <c r="C104" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D104" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E104" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2227,7 +2064,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2249,7 +2086,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2266,241 +2103,241 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2513,150 +2350,150 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>53</v>
+        <v>163</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2669,7 +2506,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2682,7 +2519,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2695,7 +2532,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -2708,7 +2545,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -2721,42 +2558,29 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="E39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="B40" s="2"/>
-      <c r="C40" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E40" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2787,7 +2611,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2796,7 +2620,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -2804,14 +2628,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E3" s="2"/>
     </row>
